--- a/Res_ConvLSTM/DroughtDataset_model_testing_1755621354_h_4.xlsx
+++ b/Res_ConvLSTM/DroughtDataset_model_testing_1755621354_h_4.xlsx
@@ -658,7 +658,7 @@
         <v>0.01785786076801291</v>
       </c>
       <c r="C2" t="n">
-        <v>99404352</v>
+        <v>6212772</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -679,49 +679,49 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>99404352</v>
+        <v>6212772</v>
       </c>
       <c r="K2" t="n">
-        <v>67541891</v>
+        <v>4344634</v>
       </c>
       <c r="L2" t="n">
-        <v>38300446</v>
+        <v>2503846</v>
       </c>
       <c r="M2" t="n">
-        <v>9545748</v>
+        <v>628661</v>
       </c>
       <c r="N2" t="n">
-        <v>520685</v>
+        <v>32114</v>
       </c>
       <c r="O2" t="n">
-        <v>5761886</v>
+        <v>384494</v>
       </c>
       <c r="P2" t="n">
-        <v>2356582</v>
+        <v>157985</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.9999180436134338</v>
+        <v>0.9999515414237976</v>
       </c>
       <c r="R2" t="n">
-        <v>0.8606384992599487</v>
+        <v>0.8858264088630676</v>
       </c>
       <c r="S2" t="n">
-        <v>0.7329989075660706</v>
+        <v>0.7662560939788818</v>
       </c>
       <c r="T2" t="n">
-        <v>0.6512104272842407</v>
+        <v>0.687294065952301</v>
       </c>
       <c r="U2" t="n">
-        <v>0.478355348110199</v>
+        <v>0.4724105894565582</v>
       </c>
       <c r="V2" t="n">
-        <v>0.70659339427948</v>
+        <v>0.7542529106140137</v>
       </c>
       <c r="W2" t="n">
-        <v>0.7646364569664001</v>
+        <v>0.8200920820236206</v>
       </c>
       <c r="X2" t="n">
-        <v>99404352</v>
+        <v>6212772</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
@@ -742,46 +742,46 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>99404352</v>
+        <v>6212772</v>
       </c>
       <c r="AF2" t="n">
-        <v>65839611</v>
+        <v>4226955</v>
       </c>
       <c r="AG2" t="n">
-        <v>35461742</v>
+        <v>2305814</v>
       </c>
       <c r="AH2" t="n">
-        <v>8673375</v>
+        <v>572610</v>
       </c>
       <c r="AI2" t="n">
-        <v>481190</v>
+        <v>30514</v>
       </c>
       <c r="AJ2" t="n">
-        <v>5299668</v>
+        <v>353874</v>
       </c>
       <c r="AK2" t="n">
-        <v>2217357</v>
+        <v>148866</v>
       </c>
       <c r="AL2" t="n">
         <v>1</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.8333726525306702</v>
+        <v>0.8560509085655212</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.6917286515235901</v>
+        <v>0.7196477651596069</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.5853376984596252</v>
+        <v>0.6182972192764282</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.3402925431728363</v>
+        <v>0.3452669084072113</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.6519567966461182</v>
+        <v>0.6965283155441284</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.7170788645744324</v>
+        <v>0.7702767848968506</v>
       </c>
     </row>
     <row r="3">
@@ -792,130 +792,130 @@
         <v>0.004485712249273131</v>
       </c>
       <c r="C3" t="n">
-        <v>2537</v>
+        <v>56</v>
       </c>
       <c r="D3" t="n">
-        <v>67541891</v>
+        <v>4344634</v>
       </c>
       <c r="E3" t="n">
-        <v>9921697</v>
+        <v>539758</v>
       </c>
       <c r="F3" t="n">
-        <v>560802</v>
+        <v>17532</v>
       </c>
       <c r="G3" t="n">
-        <v>68605</v>
+        <v>3539</v>
       </c>
       <c r="H3" t="n">
-        <v>55016</v>
+        <v>419</v>
       </c>
       <c r="I3" t="n">
-        <v>9101</v>
+        <v>86</v>
       </c>
       <c r="J3" t="n">
-        <v>157713903</v>
+        <v>9857327</v>
       </c>
       <c r="K3" t="n">
-        <v>168029828</v>
+        <v>10604399</v>
       </c>
       <c r="L3" t="n">
-        <v>191214568</v>
+        <v>12076524</v>
       </c>
       <c r="M3" t="n">
-        <v>237087490</v>
+        <v>14854143</v>
       </c>
       <c r="N3" t="n">
-        <v>255136530</v>
+        <v>15945844</v>
       </c>
       <c r="O3" t="n">
-        <v>246576040</v>
+        <v>15435873</v>
       </c>
       <c r="P3" t="n">
-        <v>253305231</v>
+        <v>15842396</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>0.8641529679298401</v>
+        <v>0.885571300983429</v>
       </c>
       <c r="S3" t="n">
-        <v>0.7371059656143188</v>
+        <v>0.7751638889312744</v>
       </c>
       <c r="T3" t="n">
-        <v>0.6395301818847656</v>
+        <v>0.6758139133453369</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3661471307277679</v>
+        <v>0.3620885908603668</v>
       </c>
       <c r="V3" t="n">
-        <v>0.7063049674034119</v>
+        <v>0.7550156712532043</v>
       </c>
       <c r="W3" t="n">
-        <v>0.761222243309021</v>
+        <v>0.8171102404594421</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>65839611</v>
+        <v>4226955</v>
       </c>
       <c r="Z3" t="n">
-        <v>11224307</v>
+        <v>634345</v>
       </c>
       <c r="AA3" t="n">
-        <v>774767</v>
+        <v>29509</v>
       </c>
       <c r="AB3" t="n">
-        <v>234653</v>
+        <v>14127</v>
       </c>
       <c r="AC3" t="n">
-        <v>73035</v>
+        <v>987</v>
       </c>
       <c r="AD3" t="n">
-        <v>13276</v>
+        <v>101</v>
       </c>
       <c r="AE3" t="n">
-        <v>157722048</v>
+        <v>9857628</v>
       </c>
       <c r="AF3" t="n">
-        <v>165802554</v>
+        <v>10453593</v>
       </c>
       <c r="AG3" t="n">
-        <v>189362180</v>
+        <v>11942041</v>
       </c>
       <c r="AH3" t="n">
-        <v>236055858</v>
+        <v>14786674</v>
       </c>
       <c r="AI3" t="n">
-        <v>254771477</v>
+        <v>15923845</v>
       </c>
       <c r="AJ3" t="n">
-        <v>246139416</v>
+        <v>15406967</v>
       </c>
       <c r="AK3" t="n">
-        <v>253155762</v>
+        <v>15832657</v>
       </c>
       <c r="AL3" t="n">
         <v>1</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.8423734307289124</v>
+        <v>0.8615846633911133</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.6824740767478943</v>
+        <v>0.7138553261756897</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.5810843706130981</v>
+        <v>0.6155587434768677</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.338374137878418</v>
+        <v>0.3440484404563904</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.649645209312439</v>
+        <v>0.6948884129524231</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.7162498831748962</v>
+        <v>0.7699460983276367</v>
       </c>
     </row>
     <row r="4">
@@ -926,285 +926,285 @@
         <v>0.05065109303700365</v>
       </c>
       <c r="C4" t="n">
-        <v>982</v>
+        <v>23</v>
       </c>
       <c r="D4" t="n">
-        <v>10104217</v>
+        <v>532236</v>
       </c>
       <c r="E4" t="n">
-        <v>38300446</v>
+        <v>2503846</v>
       </c>
       <c r="F4" t="n">
-        <v>2922765</v>
+        <v>173924</v>
       </c>
       <c r="G4" t="n">
-        <v>120467</v>
+        <v>5892</v>
       </c>
       <c r="H4" t="n">
-        <v>444497</v>
+        <v>13065</v>
       </c>
       <c r="I4" t="n">
-        <v>67196</v>
+        <v>1100</v>
       </c>
       <c r="J4" t="n">
-        <v>8145</v>
+        <v>301</v>
       </c>
       <c r="K4" t="n">
-        <v>10936923</v>
+        <v>559977</v>
       </c>
       <c r="L4" t="n">
-        <v>13951262</v>
+        <v>763790</v>
       </c>
       <c r="M4" t="n">
-        <v>5112721</v>
+        <v>286029</v>
       </c>
       <c r="N4" t="n">
-        <v>567805</v>
+        <v>35865</v>
       </c>
       <c r="O4" t="n">
-        <v>2392572</v>
+        <v>125274</v>
       </c>
       <c r="P4" t="n">
-        <v>725382</v>
+        <v>34658</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.9999590516090393</v>
+        <v>0.9999757409095764</v>
       </c>
       <c r="R4" t="n">
-        <v>0.8623921275138855</v>
+        <v>0.8856988549232483</v>
       </c>
       <c r="S4" t="n">
-        <v>0.7350466847419739</v>
+        <v>0.7706842422485352</v>
       </c>
       <c r="T4" t="n">
-        <v>0.6453174352645874</v>
+        <v>0.6815056800842285</v>
       </c>
       <c r="U4" t="n">
-        <v>0.414796769618988</v>
+        <v>0.409957230091095</v>
       </c>
       <c r="V4" t="n">
-        <v>0.7064492106437683</v>
+        <v>0.7546341419219971</v>
       </c>
       <c r="W4" t="n">
-        <v>0.7629255056381226</v>
+        <v>0.8185984492301941</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>12109531</v>
+        <v>674862</v>
       </c>
       <c r="Z4" t="n">
-        <v>35461742</v>
+        <v>2305814</v>
       </c>
       <c r="AA4" t="n">
-        <v>3515931</v>
+        <v>212641</v>
       </c>
       <c r="AB4" t="n">
-        <v>238664</v>
+        <v>13807</v>
       </c>
       <c r="AC4" t="n">
-        <v>548025</v>
+        <v>20791</v>
       </c>
       <c r="AD4" t="n">
-        <v>86677</v>
+        <v>2171</v>
       </c>
       <c r="AE4" t="n">
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>13164197</v>
+        <v>710783</v>
       </c>
       <c r="AG4" t="n">
-        <v>15803650</v>
+        <v>898273</v>
       </c>
       <c r="AH4" t="n">
-        <v>6144353</v>
+        <v>353498</v>
       </c>
       <c r="AI4" t="n">
-        <v>932858</v>
+        <v>57864</v>
       </c>
       <c r="AJ4" t="n">
-        <v>2829196</v>
+        <v>154180</v>
       </c>
       <c r="AK4" t="n">
-        <v>874851</v>
+        <v>44397</v>
       </c>
       <c r="AL4" t="n">
         <v>1</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.8378489017486572</v>
+        <v>0.8588088154792786</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.6870701909065247</v>
+        <v>0.71673983335495</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.5832032561302185</v>
+        <v>0.6169249415397644</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.3393306136131287</v>
+        <v>0.3446566164493561</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.6507989764213562</v>
+        <v>0.695707380771637</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.71666419506073</v>
+        <v>0.7701113820075989</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>1524</v>
+        <v>51</v>
       </c>
       <c r="D5" t="n">
-        <v>587216</v>
+        <v>16675</v>
       </c>
       <c r="E5" t="n">
-        <v>3242239</v>
+        <v>195660</v>
       </c>
       <c r="F5" t="n">
-        <v>9545748</v>
+        <v>628661</v>
       </c>
       <c r="G5" t="n">
-        <v>206895</v>
+        <v>14478</v>
       </c>
       <c r="H5" t="n">
-        <v>1180461</v>
+        <v>69451</v>
       </c>
       <c r="I5" t="n">
-        <v>162106</v>
+        <v>5252</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>10617758</v>
+        <v>561390</v>
       </c>
       <c r="L5" t="n">
-        <v>13660124</v>
+        <v>726240</v>
       </c>
       <c r="M5" t="n">
-        <v>5380441</v>
+        <v>301567</v>
       </c>
       <c r="N5" t="n">
-        <v>901380</v>
+        <v>56577</v>
       </c>
       <c r="O5" t="n">
-        <v>2395902</v>
+        <v>124759</v>
       </c>
       <c r="P5" t="n">
-        <v>739205</v>
+        <v>35361</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.9999683499336243</v>
+        <v>0.9999812841415405</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9161708950996399</v>
+        <v>0.9302216172218323</v>
       </c>
       <c r="S5" t="n">
-        <v>0.8926154971122742</v>
+        <v>0.9072811007499695</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9591906666755676</v>
+        <v>0.9634361267089844</v>
       </c>
       <c r="U5" t="n">
-        <v>0.9942861199378967</v>
+        <v>0.9942476749420166</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9813769459724426</v>
+        <v>0.9844413995742798</v>
       </c>
       <c r="W5" t="n">
-        <v>0.9943040013313293</v>
+        <v>0.9956429600715637</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>745156</v>
+        <v>23010</v>
       </c>
       <c r="Z5" t="n">
-        <v>3661435</v>
+        <v>226432</v>
       </c>
       <c r="AA5" t="n">
-        <v>8673375</v>
+        <v>572610</v>
       </c>
       <c r="AB5" t="n">
-        <v>257668</v>
+        <v>16757</v>
       </c>
       <c r="AC5" t="n">
-        <v>1388623</v>
+        <v>83037</v>
       </c>
       <c r="AD5" t="n">
-        <v>199932</v>
+        <v>8382</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>12320038</v>
+        <v>679069</v>
       </c>
       <c r="AG5" t="n">
-        <v>16498828</v>
+        <v>924272</v>
       </c>
       <c r="AH5" t="n">
-        <v>6252814</v>
+        <v>357618</v>
       </c>
       <c r="AI5" t="n">
-        <v>940875</v>
+        <v>58177</v>
       </c>
       <c r="AJ5" t="n">
-        <v>2858120</v>
+        <v>155379</v>
       </c>
       <c r="AK5" t="n">
-        <v>878430</v>
+        <v>44480</v>
       </c>
       <c r="AL5" t="n">
         <v>1</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.9008883237838745</v>
+        <v>0.9135147929191589</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.8743712306022644</v>
+        <v>0.8865899443626404</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.951785683631897</v>
+        <v>0.9557499289512634</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.9927127957344055</v>
+        <v>0.9927791953086853</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.9778812527656555</v>
+        <v>0.9807373285293579</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.9931812286376953</v>
+        <v>0.9944695234298706</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>2095</v>
+        <v>119</v>
       </c>
       <c r="D6" t="n">
-        <v>178743</v>
+        <v>10980</v>
       </c>
       <c r="E6" t="n">
-        <v>248932</v>
+        <v>15127</v>
       </c>
       <c r="F6" t="n">
-        <v>286540</v>
+        <v>18123</v>
       </c>
       <c r="G6" t="n">
-        <v>520685</v>
+        <v>32114</v>
       </c>
       <c r="H6" t="n">
-        <v>158090</v>
+        <v>10870</v>
       </c>
       <c r="I6" t="n">
-        <v>26980</v>
+        <v>1358</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -1224,22 +1224,22 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>215080</v>
+        <v>12528</v>
       </c>
       <c r="Z6" t="n">
-        <v>250317</v>
+        <v>14491</v>
       </c>
       <c r="AA6" t="n">
-        <v>266489</v>
+        <v>18090</v>
       </c>
       <c r="AB6" t="n">
-        <v>481190</v>
+        <v>30514</v>
       </c>
       <c r="AC6" t="n">
-        <v>177418</v>
+        <v>11381</v>
       </c>
       <c r="AD6" t="n">
-        <v>31571</v>
+        <v>1687</v>
       </c>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
@@ -1260,25 +1260,25 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>635</v>
+        <v>29</v>
       </c>
       <c r="D7" t="n">
-        <v>62074</v>
+        <v>48</v>
       </c>
       <c r="E7" t="n">
-        <v>486649</v>
+        <v>12634</v>
       </c>
       <c r="F7" t="n">
-        <v>1235410</v>
+        <v>73941</v>
       </c>
       <c r="G7" t="n">
-        <v>151135</v>
+        <v>11245</v>
       </c>
       <c r="H7" t="n">
-        <v>5761886</v>
+        <v>384494</v>
       </c>
       <c r="I7" t="n">
-        <v>459999</v>
+        <v>26862</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -1298,22 +1298,22 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>86607</v>
+        <v>328</v>
       </c>
       <c r="Z7" t="n">
-        <v>601664</v>
+        <v>21886</v>
       </c>
       <c r="AA7" t="n">
-        <v>1450551</v>
+        <v>89027</v>
       </c>
       <c r="AB7" t="n">
-        <v>175903</v>
+        <v>12082</v>
       </c>
       <c r="AC7" t="n">
-        <v>5299668</v>
+        <v>353874</v>
       </c>
       <c r="AD7" t="n">
-        <v>543395</v>
+        <v>32056</v>
       </c>
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr"/>
@@ -1334,25 +1334,25 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>372</v>
+        <v>23</v>
       </c>
       <c r="D8" t="n">
-        <v>4673</v>
+        <v>38</v>
       </c>
       <c r="E8" t="n">
-        <v>51745</v>
+        <v>611</v>
       </c>
       <c r="F8" t="n">
-        <v>107204</v>
+        <v>2509</v>
       </c>
       <c r="G8" t="n">
-        <v>20703</v>
+        <v>711</v>
       </c>
       <c r="H8" t="n">
-        <v>554508</v>
+        <v>31469</v>
       </c>
       <c r="I8" t="n">
-        <v>2356582</v>
+        <v>157985</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -1372,22 +1372,22 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>7823</v>
+        <v>55</v>
       </c>
       <c r="Z8" t="n">
-        <v>65927</v>
+        <v>1119</v>
       </c>
       <c r="AA8" t="n">
-        <v>136615</v>
+        <v>4231</v>
       </c>
       <c r="AB8" t="n">
-        <v>25970</v>
+        <v>1091</v>
       </c>
       <c r="AC8" t="n">
-        <v>642095</v>
+        <v>37984</v>
       </c>
       <c r="AD8" t="n">
-        <v>2217357</v>
+        <v>148866</v>
       </c>
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr"/>
